--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45931</v>
+        <v>45264</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,45 +1201,158 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,153 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46279</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1911,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1923,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2918,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45614</v>
+        <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,8 +3020,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3069,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3068,10 +3083,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3098,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3142,14 +3152,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3171,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3215,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3237,11 +3242,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3573-2026</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,31 +1088,31 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,242 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1135,266 +1365,36 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46280</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>44944</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,22 +2003,17 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2028,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2042,49 +2037,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,14 +2089,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44944</v>
+        <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,17 +2108,22 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>8.699999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2147,42 +2147,42 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45632</v>
+        <v>44894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2708,13 +2708,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2752,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2766,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2792,7 +2787,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2830,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2852,7 +2847,7 @@
         <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2870,7 +2865,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2918,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>45237</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2948,7 +2943,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2986,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +3000,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3021,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3069,7 +3064,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3083,10 +3078,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3099,7 +3094,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3137,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3152,14 +3147,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3167,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3215,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44894</v>
+        <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3245,7 +3240,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3288,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3302,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3317,8 +3312,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3378,7 +3378,7 @@
         <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45931</v>
+        <v>46042</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,22 +1201,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1225,21 +1225,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,153 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1911,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1923,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44944</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,17 +2003,22 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>8.699999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2028,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2037,49 +2042,49 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2089,14 +2094,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45229</v>
+        <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2108,22 +2113,17 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2147,42 +2147,42 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2708,8 +2708,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2752,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2766,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2787,7 +2792,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2830,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2847,7 +2852,7 @@
         <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2865,7 +2870,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2918,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45237</v>
+        <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2943,7 +2948,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2986,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3000,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3021,7 +3026,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3064,7 +3069,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3078,10 +3083,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45632</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3094,7 +3099,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3137,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3147,14 +3152,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3167,7 +3172,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3215,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44645</v>
+        <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3240,7 +3245,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3283,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,10 +3302,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3312,13 +3317,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3378,7 +3378,7 @@
         <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 47571-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>45931</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,45 +1088,162 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,111 +1252,111 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 3573-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>46042</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>VÄRMLANDS LÄN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>4.3</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>16</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1248,153 +1365,36 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46282</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45632</v>
+        <v>44894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2864,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2918,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,13 +2937,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3020,13 +3010,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3069,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3083,10 +3068,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,8 +3083,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3152,14 +3142,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3171,8 +3161,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3215,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3242,6 +3237,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45931</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,45 +1088,158 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>11</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1135,153 +1248,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46283</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>46042</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1911,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1923,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2918,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45614</v>
+        <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,8 +3020,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3069,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3068,10 +3083,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3098,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3142,14 +3152,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3171,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3215,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3237,11 +3242,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46042</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46042</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,125 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,111 +1248,111 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 47571-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>45931</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>VÄRMLANDS LÄN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,153 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46288</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45218</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,8 +2562,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2623,7 +2628,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2679,7 +2684,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2698,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2708,13 +2713,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2845,14 +2845,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45237</v>
+        <v>45544</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2864,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2918,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,13 +2937,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3016,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3069,7 +3059,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3083,10 +3073,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,8 +3088,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3137,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3152,14 +3147,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3171,8 +3166,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3232,7 +3232,7 @@
         <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3573-2026</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,31 +1088,31 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,242 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1135,266 +1365,36 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46289</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1911,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1923,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45218</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,13 +2562,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2628,7 +2623,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45614</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,8 +2708,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2845,14 +2845,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45544</v>
+        <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2918,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44645</v>
+        <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3016,7 +3026,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3059,7 +3069,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3073,10 +3083,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3088,13 +3098,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3137,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3147,14 +3152,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3166,13 +3171,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3232,7 +3232,7 @@
         <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,242 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46291</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,266 +1365,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>11</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46290</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45632</v>
+        <v>44894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2864,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2918,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,13 +2937,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3020,13 +3010,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3069,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3083,10 +3068,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,8 +3083,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3152,14 +3142,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3171,8 +3161,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3215,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3242,6 +3237,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45264</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>44894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45264</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>44894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3573-2026</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,31 +1088,31 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,125 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1135,111 +1248,111 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 47571-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>45931</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>VÄRMLANDS LÄN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,153 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1911,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1923,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2918,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45614</v>
+        <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,8 +3020,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3069,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3068,10 +3083,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3098,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3142,14 +3152,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3171,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3215,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3237,11 +3242,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,242 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,266 +1365,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>16</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45632</v>
+        <v>44894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2864,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2918,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,13 +2937,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3020,13 +3010,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3069,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3083,10 +3068,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,8 +3083,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3152,14 +3142,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3171,8 +3161,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3215,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3242,6 +3237,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3573-2026</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,31 +1088,31 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,125 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1135,111 +1248,111 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 47571-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>45931</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>VÄRMLANDS LÄN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,160 +1361,47 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24616-2022</t>
+          <t>A 24618-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1469,172 +1469,172 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Svart skogssnigel
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24616-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>21</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>20</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tretåig hackspett
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24618-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46295</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Svart skogssnigel
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
         <v/>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,14 +2094,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44944</v>
+        <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,17 +2113,22 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>8.699999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2147,49 +2152,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2204,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>44944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2218,22 +2223,17 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2257,42 +2257,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,11 +2408,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,8 +2562,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2611,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2625,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44894</v>
+        <v>44645</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2641,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2684,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2698,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2719,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2762,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2767,14 +2772,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>45218</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2792,7 +2797,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2840,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2854,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45632</v>
+        <v>45247</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,8 +2869,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2918,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2922,10 +2932,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45614</v>
+        <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,8 +2947,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2996,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3010,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,8 +3025,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3074,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3068,10 +3088,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3085,11 +3105,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3152,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3166,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3181,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3225,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3239,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,13 +3254,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3288,7 +3298,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3298,14 +3308,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44645</v>
+        <v>45544</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3328,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3371,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3385,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3390,13 +3400,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3444,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3458,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,13 +3473,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,242 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,273 +1365,43 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>16</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24618-2022</t>
+          <t>A 24616-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1469,172 +1469,172 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>21</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Tretåig hackspett
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24618-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart skogssnigel
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24616-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46296</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21</v>
-      </c>
-      <c r="U10" t="n">
-        <v>20</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Tretåig hackspett
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
         <v/>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,14 +2094,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45229</v>
+        <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,22 +2113,17 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2152,49 +2147,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2204,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44944</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,17 +2218,22 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.699999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2257,42 +2257,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,11 +2408,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,13 +2562,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2611,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2625,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44645</v>
+        <v>44894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2641,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2684,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2719,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2762,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2772,14 +2767,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45218</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2797,7 +2792,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2840,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2854,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45247</v>
+        <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2869,13 +2864,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2918,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2932,10 +2922,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2947,13 +2937,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2996,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3010,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3025,13 +3010,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3074,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3088,10 +3068,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3105,11 +3085,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3152,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3166,10 +3146,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3181,8 +3161,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3225,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3239,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45614</v>
+        <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3254,8 +3239,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.4</v>
+        <v>0.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3298,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3308,14 +3298,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45544</v>
+        <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3328,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3371,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3385,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3400,8 +3390,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.6</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3444,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3458,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3473,8 +3468,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45931</v>
+        <v>45264</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,45 +1201,158 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46298</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,153 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46297</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1911,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1923,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2918,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45614</v>
+        <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,8 +3020,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3069,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3068,10 +3083,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3098,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3142,14 +3152,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3171,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3215,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3237,11 +3242,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45264</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45931</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45264</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45931</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3232,7 +3232,7 @@
         <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 47571-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45264</v>
+        <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,45 +1201,162 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1248,153 +1365,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46300</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45632</v>
+        <v>44894</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2864,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2918,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,13 +2937,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3020,13 +3010,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3069,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3083,10 +3068,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,8 +3083,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3152,14 +3142,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3171,8 +3161,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3215,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3242,6 +3237,11 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45931</v>
+        <v>45264</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,45 +1201,158 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,153 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46301</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1911,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1923,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2918,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45614</v>
+        <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,8 +3020,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3069,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3068,10 +3083,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3098,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3142,14 +3152,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3171,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3215,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3229,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3237,11 +3242,6 @@
       <c r="G29" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I29" t="n">
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3573-2026</t>
+          <t>A 47571-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>45931</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,22 +1088,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1112,21 +1112,251 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1135,266 +1365,36 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46302</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,20 +1894,25 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1922,59 +1927,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1985,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,13 +2004,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2021,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2033,51 +2029,55 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2472,7 +2472,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45218</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,8 +2562,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2623,7 +2628,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2679,7 +2684,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2698,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2708,13 +2713,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2845,14 +2845,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45237</v>
+        <v>45544</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2864,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2918,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,13 +2937,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3016,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3069,7 +3059,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3083,10 +3073,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,8 +3088,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3137,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3152,14 +3147,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3171,8 +3166,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3232,7 +3232,7 @@
         <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45931</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,45 +1088,158 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>11</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1135,153 +1248,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46303</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>46042</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,25 +1894,20 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1927,55 +1922,59 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1985,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45632</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2004,8 +2003,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2017,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2029,55 +2033,51 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,35 +2264,35 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2472,7 +2472,7 @@
         <v>45237</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2543,14 +2543,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45218</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,13 +2562,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2628,7 +2623,7 @@
         <v>45632</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2684,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45614</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,8 +2708,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2788,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2845,14 +2845,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45544</v>
+        <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2918,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44645</v>
+        <v>45218</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3016,7 +3026,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3059,7 +3069,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3073,10 +3083,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3088,13 +3098,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3137,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3147,14 +3152,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3166,13 +3171,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3232,7 +3232,7 @@
         <v>44894</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3305,7 +3305,7 @@
         <v>44645</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3470,11 +3470,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45931</v>
+        <v>46042</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,22 +1201,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="J7" t="n">
         <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
         <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1225,21 +1225,134 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46305</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,153 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1830,42 +1830,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,20 +1894,25 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1922,59 +1927,55 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1985,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,13 +2004,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2021,7 +2017,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2033,58 +2029,62 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44944</v>
+        <v>45176</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,17 +2113,22 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2147,49 +2152,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2203,10 +2208,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>44944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2218,13 +2223,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2268,31 +2268,31 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,11 +2486,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45632</v>
+        <v>45614</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.6</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2710,11 +2710,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,13 +2786,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2830,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2844,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45237</v>
+        <v>44645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2859,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2903,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2913,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2944,11 +2934,11 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3026,7 +3016,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3069,7 +3059,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3083,10 +3073,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3098,8 +3088,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3137,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3152,14 +3147,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45544</v>
+        <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3172,7 +3167,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3215,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3229,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44894</v>
+        <v>45176</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3244,8 +3239,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3302,10 +3302,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44645</v>
+        <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3317,8 +3317,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3366,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3380,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3390,13 +3395,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>46042</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45931</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>45176</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45614</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45247</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45544</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>44645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45176</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45237</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>46042</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1301,7 +1301,7 @@
         <v>45931</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45229</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1992,7 +1992,7 @@
         <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>45176</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         <v>44944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>44481</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>45614</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45247</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45544</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2847,7 +2847,7 @@
         <v>44645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2920,7 +2920,7 @@
         <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2998,7 +2998,7 @@
         <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45176</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45237</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3534,7 +3534,7 @@
         <v>45415</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE33"/>
+  <dimension ref="A1:AE32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,242 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,266 +1365,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>16</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1765,14 +1765,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45229</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1830,42 +1830,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,25 +1894,20 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1927,55 +1922,59 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1985,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45632</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2004,8 +2003,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2017,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2029,62 +2033,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2098,10 +2098,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45176</v>
+        <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,22 +2113,17 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2143,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2152,49 +2147,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44944</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,8 +2218,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.699999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2268,38 +2268,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56835-2021</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44481</v>
+        <v>44645</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,13 +2328,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>18.8</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2377,7 +2372,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2382,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,11 +2403,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2450,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2464,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2486,11 +2481,11 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2528,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2547,10 +2542,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45632</v>
+        <v>45182</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,8 +2557,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45614</v>
+        <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2635,8 +2635,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2684,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2698,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45247</v>
+        <v>45614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2708,13 +2713,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2767,14 +2767,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45544</v>
+        <v>45632</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2830,7 +2830,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,8 +2859,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2903,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2920,7 +2925,7 @@
         <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2938,7 +2943,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2986,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3012,11 +3017,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.3</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3059,7 +3064,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3069,14 +3074,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3090,11 +3095,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3137,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3151,10 +3156,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44894</v>
+        <v>45176</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3166,8 +3171,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3220,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3234,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45176</v>
+        <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,13 +3249,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3288,7 +3293,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3298,14 +3303,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45237</v>
+        <v>45544</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3317,13 +3322,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44645</v>
+        <v>44894</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3436,27 +3436,27 @@
       </c>
       <c r="V31" s="2" t="inlineStr"/>
     </row>
-    <row r="32" ht="15" customHeight="1">
+    <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>S 1429-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45237</v>
+        <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3468,13 +3468,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3513,79 +3508,6 @@
         <v>0</v>
       </c>
       <c r="V32" s="2" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>S 1429-2024</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D33" s="1" t="n">
-        <v>45415</v>
-      </c>
-      <c r="E33" s="1" t="n">
-        <v>46307</v>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>2</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45264</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44645</v>
+        <v>45218</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,8 +2328,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2372,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2386,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2403,11 +2408,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2450,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2460,14 +2465,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2479,13 +2484,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2557,13 +2557,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2601,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2615,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45237</v>
+        <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2637,11 +2632,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2684,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45614</v>
+        <v>45237</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,8 +2708,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>45632</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,13 +2859,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2903,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,13 +2932,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2986,7 +2976,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3000,10 +2990,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3017,11 +3007,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3064,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3074,14 +3064,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3095,11 +3085,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3156,10 +3146,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3167,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3237,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3303,14 +3293,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45544</v>
+        <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,8 +3312,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3380,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,8 +3390,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3573-2026</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,31 +1088,31 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,242 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1135,273 +1365,43 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>11</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24616-2022</t>
+          <t>A 24618-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1469,172 +1469,172 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Svart skogssnigel
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24616-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>21</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>20</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tretåig hackspett
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24618-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46309</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Svart skogssnigel
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
         <v/>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1874,14 +1875,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1899,7 +1900,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1939,42 +1940,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1989,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,25 +2004,20 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2036,48 +2032,52 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45218</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,11 +2408,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2710,11 +2710,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,8 +2786,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2830,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2840,14 +2845,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45614</v>
+        <v>45218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2903,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2917,10 +2927,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2976,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2990,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,13 +3020,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3064,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3064,14 +3074,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3093,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3137,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3151,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3159,11 +3164,6 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -3210,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3227,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3314,11 +3314,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 47571-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>45931</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,45 +1088,162 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,153 +1252,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>11</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>46042</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24618-2022</t>
+          <t>A 24616-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1469,172 +1469,172 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>21</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Tretåig hackspett
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24618-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart skogssnigel
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24616-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46310</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21</v>
-      </c>
-      <c r="U10" t="n">
-        <v>20</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Tretåig hackspett
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
         <v/>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45237</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,20 +1786,20 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1830,42 +1830,42 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1875,14 +1875,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1912,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1924,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1989,10 +1988,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2004,8 +2003,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2017,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2029,55 +2033,51 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2316,7 +2316,7 @@
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45614</v>
+        <v>45247</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,8 +2484,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2545,7 +2550,7 @@
         <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2601,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2615,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2630,13 +2635,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2708,13 +2708,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2752,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2766,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>44645</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,13 +2781,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2825,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2845,14 +2835,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2866,11 +2856,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2903,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2927,10 +2917,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2948,7 +2938,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3020,8 +3010,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3064,7 +3059,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3074,14 +3069,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45544</v>
+        <v>44894</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3094,7 +3089,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3137,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3151,10 +3146,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44894</v>
+        <v>45176</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3166,8 +3161,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3227,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3314,11 +3314,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45931</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,45 +1088,158 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46312</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>11</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1135,153 +1248,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46311</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>8</v>
-      </c>
-      <c r="U7" t="n">
-        <v>4</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>46042</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45237</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1786,20 +1786,20 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1814,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1830,35 +1830,35 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
@@ -1882,7 +1882,7 @@
         <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45176</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,11 +2330,11 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45247</v>
+        <v>45614</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,13 +2484,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.7</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2550,7 +2545,7 @@
         <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2606,7 +2601,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2615,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45614</v>
+        <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2635,8 +2630,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>3.4</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2689,14 +2689,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2708,8 +2708,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2752,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2766,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44645</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2781,8 +2786,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2825,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2835,14 +2845,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2856,11 +2866,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2903,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2917,10 +2927,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2938,7 +2948,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,13 +3020,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3059,7 +3064,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3069,14 +3074,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44894</v>
+        <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3089,7 +3094,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3137,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3151,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45176</v>
+        <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3166,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3227,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3314,11 +3314,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46042</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45614</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45176</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45247</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>46042</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1882,7 +1882,7 @@
         <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45614</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2545,7 +2545,7 @@
         <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2696,7 @@
         <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45176</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3154,7 +3154,7 @@
         <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3378,7 +3378,7 @@
         <v>45247</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 47571-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>45931</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,45 +1088,275 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3</v>
       </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>4</v>
-      </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>16</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,266 +1365,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>11</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>16</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45237</v>
+        <v>45247</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45632</v>
+        <v>44894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2710,11 +2710,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,13 +2786,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2830,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2845,14 +2840,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45218</v>
+        <v>45614</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2859,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2903,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2927,10 +2917,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45176</v>
+        <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,13 +2932,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2976,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2990,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3020,8 +3005,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3064,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3074,14 +3064,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3093,8 +3083,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3137,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3151,10 +3146,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3164,6 +3159,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -3210,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3227,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3314,11 +3314,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45931</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,22 +1088,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1112,21 +1112,247 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1135,266 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>16</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46315</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1893,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1911,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1923,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45544</v>
+        <v>45614</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2710,11 +2710,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45632</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,8 +2786,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2830,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2840,14 +2845,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45614</v>
+        <v>45218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2903,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2917,10 +2927,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2976,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2990,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,13 +3020,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3064,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3064,14 +3074,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3093,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3137,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3151,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3159,11 +3164,6 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -3210,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3227,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3314,11 +3314,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45247</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 47571-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45264</v>
+        <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,45 +1201,162 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1248,153 +1365,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46316</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I17" t="n">
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45237</v>
+        <v>45247</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45632</v>
+        <v>44894</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2615,10 +2615,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2710,11 +2710,11 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>3.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,13 +2786,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2830,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2845,14 +2840,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45218</v>
+        <v>45614</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2864,13 +2859,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2903,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2927,10 +2917,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45176</v>
+        <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,13 +2932,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2991,7 +2976,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3005,10 +2990,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3020,8 +3005,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3064,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3074,14 +3064,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45544</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3093,8 +3083,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.3</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3137,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3151,10 +3146,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3164,6 +3159,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -3210,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3227,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3240,7 +3240,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.6</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3314,11 +3314,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3573-2026</t>
+          <t>A 47571-2025</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>45931</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,22 +1088,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1112,21 +1112,138 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>11</v>
+      </c>
+      <c r="U6" t="n">
+        <v>11</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1135,153 +1252,36 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46317</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>11</v>
-      </c>
-      <c r="U7" t="n">
-        <v>11</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>45264</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,8 +1784,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1797,7 +1802,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1809,62 +1814,58 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1895,20 +1896,20 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1923,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1939,42 +1940,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1989,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2003,25 +2004,20 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2036,55 +2032,59 @@
         <v>1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z14">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,14 +2094,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44944</v>
+        <v>45229</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2113,17 +2113,22 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>8.699999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2138,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2147,49 +2152,49 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2204,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>44944</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2218,22 +2223,17 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2257,42 +2257,42 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
@@ -2316,7 +2316,7 @@
         <v>45218</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2391,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45247</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,11 +2408,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2465,14 +2465,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45544</v>
+        <v>45176</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2484,8 +2484,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2528,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2542,10 +2547,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44894</v>
+        <v>44645</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2558,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2601,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2611,14 +2616,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45176</v>
+        <v>45544</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2630,13 +2635,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>1.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2679,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45237</v>
+        <v>44894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2708,13 +2708,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>3.2</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2752,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2766,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45632</v>
+        <v>44645</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2825,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2844,10 +2839,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45614</v>
+        <v>45182</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,8 +2854,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>0.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2917,10 +2917,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44645</v>
+        <v>45247</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,8 +2932,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2976,7 +2981,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2990,10 +2995,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3007,11 +3012,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3059,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3068,10 +3073,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3088,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45632</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3161,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3205,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3219,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44645</v>
+        <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,8 +3234,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3283,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3297,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3314,11 +3314,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3392,11 +3392,11 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45931</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,22 +1088,22 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>8.300000000000001</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
         <v>4</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
       </c>
       <c r="N6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1112,21 +1112,134 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>11</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1135,153 +1248,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE6">
+      <c r="AE7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>16</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
         <v>45264</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24616-2022</t>
+          <t>A 24618-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="J9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1469,172 +1469,172 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>3</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Svart skogssnigel
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24616-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46319</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3</v>
+      </c>
+      <c r="T10" t="n">
         <v>21</v>
       </c>
-      <c r="U9" t="n">
+      <c r="U10" t="n">
         <v>20</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Tretåig hackspett
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24618-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46318</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="J10" t="n">
-        <v>2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Svart skogssnigel
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
         <v/>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>44944</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,22 +1784,17 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1814,7 +1809,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1823,49 +1818,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1875,14 +1870,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1896,20 +1891,20 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1924,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1940,35 +1935,35 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
@@ -1992,7 +1987,7 @@
         <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2084,7 +2079,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,14 +2089,14 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45229</v>
+        <v>45176</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2119,7 +2114,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.3</v>
+        <v>1.8</v>
       </c>
       <c r="J15" t="n">
         <v>1</v>
@@ -2159,42 +2154,42 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2208,10 +2203,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44944</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2223,8 +2218,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>8.699999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
@@ -2268,38 +2268,38 @@
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2309,14 +2309,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45218</v>
+        <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2377,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2387,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -2455,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2547,10 +2547,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44645</v>
+        <v>45247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2562,8 +2562,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2623,7 +2628,7 @@
         <v>45544</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2696,7 +2701,7 @@
         <v>44894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2752,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2766,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44645</v>
+        <v>45176</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2781,8 +2786,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2825,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2839,10 +2849,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2856,11 +2866,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.8</v>
+        <v>3.2</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2903,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2917,10 +2927,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45247</v>
+        <v>45632</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2932,13 +2942,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2981,7 +2986,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2995,10 +3000,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45237</v>
+        <v>45614</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3010,13 +3015,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3073,10 +3073,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45614</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3089,7 +3089,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.4</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3146,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45632</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,8 +3161,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>1.6</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3222,7 +3227,7 @@
         <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3300,7 +3305,7 @@
         <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3361,7 +3366,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3380,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45237</v>
+        <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3390,13 +3395,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>3.2</v>
+        <v>1.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45264</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>44944</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>45176</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45544</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>44894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45176</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45632</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45614</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1188,7 +1188,7 @@
         <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1305,7 +1305,7 @@
         <v>45264</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1772,7 +1772,7 @@
         <v>44944</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
         <v>45229</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45632</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2096,7 +2096,7 @@
         <v>45176</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>45237</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2394,7 +2394,7 @@
         <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2550,7 @@
         <v>45247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2628,7 +2628,7 @@
         <v>45544</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
         <v>44894</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>45176</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
         <v>45237</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         <v>45632</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3003,7 +3003,7 @@
         <v>45614</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3227,7 +3227,7 @@
         <v>45182</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3305,7 +3305,7 @@
         <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3383,7 +3383,7 @@
         <v>44645</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 3573-2026</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>46042</v>
+        <v>45264</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,31 +1088,31 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.3</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
         <v>4</v>
-      </c>
-      <c r="K6" t="n">
-        <v>1</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,125 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>8</v>
+      </c>
+      <c r="U6" t="n">
+        <v>4</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 3573-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>16</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Jättesvampmal
@@ -1135,111 +1248,111 @@
 Vanlig padda</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
         <is>
           <t>A 47571-2025</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>avverkningsanmälan</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Föryngringsavverkning</t>
         </is>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D8" s="1" t="n">
         <v>45931</v>
       </c>
-      <c r="E7" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F7" t="inlineStr">
+      <c r="E8" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F8" t="inlineStr">
         <is>
           <t>VÄRMLANDS LÄN</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="I8" t="n">
         <v>8.300000000000001</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J8" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
         <v>3</v>
       </c>
-      <c r="R7" t="n">
+      <c r="R8" t="n">
         <v>2</v>
       </c>
-      <c r="S7" t="n">
+      <c r="S8" t="n">
         <v>5</v>
       </c>
-      <c r="T7" t="n">
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,160 +1361,47 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 24618-2022</t>
+          <t>A 24616-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1436,10 +1436,10 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1469,172 +1469,172 @@
         <v>3</v>
       </c>
       <c r="T9" t="n">
+        <v>21</v>
+      </c>
+      <c r="U9" t="n">
+        <v>20</v>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Tretåig hackspett
+Spillkråka</t>
+        </is>
+      </c>
+      <c r="W9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="X9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="Y9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="Z9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AA9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AB9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AC9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AD9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+      <c r="AE9">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" ht="15" customHeight="1">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>A 24618-2022</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>44727</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J10" t="n">
+        <v>2</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" t="n">
         <v>3</v>
       </c>
-      <c r="U9" t="n">
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
         <v>2</v>
       </c>
-      <c r="V9" s="2" t="inlineStr">
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Svart skogssnigel
 Spillkråka</t>
         </is>
       </c>
-      <c r="W9">
+      <c r="W10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24618-2022 artfynd.xlsx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="X9">
+      <c r="X10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24618-2022 karta.png", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="Y9">
+      <c r="Y10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24618-2022 georefererad karta.tif", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="Z9">
+      <c r="Z10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24618-2022 karta knärot.png", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AA9">
+      <c r="AA10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24618-2022 FSC-klagomål.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AB9">
+      <c r="AB10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24618-2022 FSC-klagomål mail.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AC9">
+      <c r="AC10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24618-2022 tillsynsbegäran.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AD9">
+      <c r="AD10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24618-2022 tillsynsbegäran mail.docx", "A 24618-2022")</f>
         <v/>
       </c>
-      <c r="AE9">
+      <c r="AE10">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24618-2022 prioriterade fågelarter.docx", "A 24618-2022")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10" ht="15" customHeight="1">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>A 24616-2022</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>44727</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46321</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1</v>
-      </c>
-      <c r="S10" t="n">
-        <v>3</v>
-      </c>
-      <c r="T10" t="n">
-        <v>21</v>
-      </c>
-      <c r="U10" t="n">
-        <v>20</v>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Tretåig hackspett
-Spillkråka</t>
-        </is>
-      </c>
-      <c r="W10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 24616-2022 artfynd.xlsx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="X10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 24616-2022 karta.png", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="Y10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 24616-2022 georefererad karta.tif", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="Z10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 24616-2022 karta knärot.png", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AA10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 24616-2022 FSC-klagomål.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AB10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 24616-2022 FSC-klagomål mail.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AC10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 24616-2022 tillsynsbegäran.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AD10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 24616-2022 tillsynsbegäran mail.docx", "A 24616-2022")</f>
-        <v/>
-      </c>
-      <c r="AE10">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 24616-2022 prioriterade fågelarter.docx", "A 24616-2022")</f>
         <v/>
       </c>
     </row>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44944</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,17 +1784,22 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1809,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1818,49 +1823,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1870,14 +1875,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45229</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1889,13 +1894,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1907,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,58 +1919,62 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1980,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45632</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1999,8 +2003,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>1.6</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2012,7 +2021,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
         <v>0</v>
@@ -2024,62 +2033,58 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2093,10 +2098,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45176</v>
+        <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2108,22 +2113,17 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -2147,42 +2147,42 @@
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
         <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45237</v>
+        <v>44645</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,13 +2328,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2377,7 +2372,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2387,14 +2382,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2408,11 +2403,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2472,7 +2467,7 @@
         <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2550,7 +2545,7 @@
         <v>45247</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2611,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2621,14 +2616,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45544</v>
+        <v>45237</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2640,8 +2635,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44894</v>
+        <v>45614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,13 +2786,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>1.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2835,7 +2830,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2849,10 +2844,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2866,11 +2861,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.2</v>
+        <v>0.3</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2908,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2927,10 +2922,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45632</v>
+        <v>45182</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,8 +2937,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2986,7 +2986,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3000,10 +3000,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45614</v>
+        <v>45237</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3015,8 +3015,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3059,7 +3064,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3069,14 +3074,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45218</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3088,8 +3093,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3142,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3156,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3167,7 +3177,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3220,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3234,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,13 +3249,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.3</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3288,7 +3293,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3298,14 +3303,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45182</v>
+        <v>45544</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3317,13 +3322,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>0.4</v>
+        <v>1.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3380,10 +3380,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44645</v>
+        <v>44894</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1058,7 +1058,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 3573-2026</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1072,10 +1072,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>45264</v>
+        <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1088,16 +1088,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>4.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>1</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R6" t="n">
         <v>1</v>
@@ -1121,12 +1121,125 @@
         <v>5</v>
       </c>
       <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Jättesvampmal
+Åkergroda
+Vanlig groda
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="X6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Y6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="Z6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AA6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AB6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AC6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+      <c r="AD6">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="15" customHeight="1">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="n">
         <v>8</v>
       </c>
-      <c r="U6" t="n">
+      <c r="U7" t="n">
         <v>4</v>
       </c>
-      <c r="V6" s="2" t="inlineStr">
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1135,149 +1248,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W6">
+      <c r="W7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X6">
+      <c r="X7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y6">
+      <c r="Y7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z6">
+      <c r="Z7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA6">
+      <c r="AA7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB6">
+      <c r="AB7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC6">
+      <c r="AC7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD6">
+      <c r="AD7">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="15" customHeight="1">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>A 3573-2026</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J7" t="n">
-        <v>4</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1</v>
-      </c>
-      <c r="S7" t="n">
-        <v>5</v>
-      </c>
-      <c r="T7" t="n">
-        <v>16</v>
-      </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Jättesvampmal
-Åkergroda
-Vanlig groda
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 3573-2026 artfynd.xlsx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="X7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 3573-2026 karta.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Y7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 3573-2026 georefererad karta.tif", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="Z7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 3573-2026 karta knärot.png", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AA7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 3573-2026 FSC-klagomål.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AB7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 3573-2026 FSC-klagomål mail.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AC7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 3573-2026 tillsynsbegäran.docx", "A 3573-2026")</f>
-        <v/>
-      </c>
-      <c r="AD7">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 3573-2026 tillsynsbegäran mail.docx", "A 3573-2026")</f>
         <v/>
       </c>
     </row>
@@ -1301,7 +1301,7 @@
         <v>45931</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45176</v>
+        <v>45632</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,13 +1784,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I12" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="J12" t="n">
         <v>1</v>
@@ -1802,7 +1797,7 @@
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1814,58 +1809,62 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z12">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1879,10 +1878,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45632</v>
+        <v>45176</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1894,8 +1893,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -1907,7 +1911,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1919,62 +1923,58 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1984,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2005,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2033,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,35 +2049,35 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
         <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2189,7 +2189,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45237</v>
+        <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.3</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44645</v>
+        <v>44894</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45218</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45182</v>
+        <v>45176</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45247</v>
+        <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.7</v>
+        <v>3.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2620,10 +2620,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45237</v>
+        <v>45247</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2694,14 +2694,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45614</v>
+        <v>45544</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.4</v>
+        <v>1.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2774,7 +2774,7 @@
         <v>45632</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2844,10 +2844,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2859,13 +2859,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>0.3</v>
+        <v>3.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2908,7 +2903,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2922,10 +2917,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2937,13 +2932,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2986,7 +2976,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3000,10 +2990,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3017,11 +3007,11 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.2</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3064,7 +3054,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3074,14 +3064,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3095,11 +3085,11 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3142,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3156,10 +3146,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3177,7 +3167,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3237,7 +3227,7 @@
         <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3293,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3303,14 +3293,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45544</v>
+        <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3322,8 +3312,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3380,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44894</v>
+        <v>45182</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,8 +3390,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 61380-2023</t>
+          <t>A 47571-2025</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45264</v>
+        <v>45931</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,45 +1201,162 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.3</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
       <c r="R7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>11</v>
+      </c>
+      <c r="U7" t="n">
+        <v>11</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Långskägg
+Knärot
+Motaggsvamp
+Tjäder
+Kungsfågel</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+      <c r="AE7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 61380-2023</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45264</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J8" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" t="n">
+        <v>3</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>4</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>8</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>4</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Blå taggsvamp
@@ -1248,153 +1365,36 @@
 Gullgröppa</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 47571-2025</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45931</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="J8" t="n">
-        <v>4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" t="n">
-        <v>1</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>11</v>
-      </c>
-      <c r="U8" t="n">
-        <v>11</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Långskägg
-Knärot
-Motaggsvamp
-Tjäder
-Kungsfågel</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-      <c r="AE8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45632</v>
+        <v>44944</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1785,19 +1785,19 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
         <v>0</v>
@@ -1812,59 +1812,55 @@
         <v>1</v>
       </c>
       <c r="R12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1878,10 +1874,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45176</v>
+        <v>45237</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1895,20 +1891,20 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1923,7 +1919,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1939,42 +1935,42 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1988,10 +1984,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45237</v>
+        <v>45176</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,20 +2001,20 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -2033,7 +2029,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -2049,42 +2045,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2098,10 +2094,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44944</v>
+        <v>45632</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2114,19 +2110,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>8.699999999999999</v>
+        <v>1.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2141,48 +2137,52 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U15" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z15">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
         <v>45229</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2299,7 +2299,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44894</v>
+        <v>45632</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2372,7 +2372,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2382,14 +2382,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2403,11 +2403,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2450,7 +2450,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2464,10 +2464,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2485,7 +2485,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2545,7 +2545,7 @@
         <v>45237</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2616,14 +2616,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45247</v>
+        <v>45218</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2684,7 +2684,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2694,14 +2694,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45544</v>
+        <v>45176</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2713,8 +2713,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2757,7 +2762,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2771,10 +2776,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45632</v>
+        <v>45182</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2786,8 +2791,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2830,7 +2840,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2844,10 +2854,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45614</v>
+        <v>44645</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2860,7 +2870,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>3.4</v>
+        <v>1.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2903,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2913,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44645</v>
+        <v>45544</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2933,7 +2943,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2976,7 +2986,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2990,10 +3000,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3005,13 +3015,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3054,7 +3059,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3068,10 +3073,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45182</v>
+        <v>44645</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3083,13 +3088,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>0.3</v>
+        <v>1.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3149,7 +3149,7 @@
         <v>45182</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44645</v>
+        <v>45247</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,8 +3239,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3300,7 +3305,7 @@
         <v>45237</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3361,7 +3366,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3375,10 +3380,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3390,13 +3395,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>

--- a/Översikt HAMMARÖ.xlsx
+++ b/Översikt HAMMARÖ.xlsx
@@ -601,7 +601,7 @@
         <v>46167</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -722,7 +722,7 @@
         <v>46167</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
         <v>44529</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -955,7 +955,7 @@
         <v>44693</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46042</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1171,7 +1171,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 47571-2025</t>
+          <t>A 61380-2023</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1185,10 +1185,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>45931</v>
+        <v>45264</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1201,45 +1201,158 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>8.300000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1</v>
-      </c>
-      <c r="N7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3</v>
-      </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
       </c>
       <c r="T7" t="n">
+        <v>8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>4</v>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Blå taggsvamp
+Gropticka
+Motaggsvamp
+Gullgröppa</t>
+        </is>
+      </c>
+      <c r="W7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="X7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Y7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="Z7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AA7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AB7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AC7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+      <c r="AD7">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" ht="15" customHeight="1">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>A 47571-2025</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>45931</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>46326</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>VÄRMLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>HAMMARÖ</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="n">
         <v>11</v>
       </c>
-      <c r="U7" t="n">
+      <c r="U8" t="n">
         <v>11</v>
       </c>
-      <c r="V7" s="2" t="inlineStr">
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>Långskägg
 Knärot
@@ -1248,153 +1361,40 @@
 Kungsfågel</t>
         </is>
       </c>
-      <c r="W7">
+      <c r="W8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 47571-2025 artfynd.xlsx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="X7">
+      <c r="X8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 47571-2025 karta.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Y7">
+      <c r="Y8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 47571-2025 georefererad karta.tif", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="Z7">
+      <c r="Z8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 47571-2025 karta knärot.png", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AA7">
+      <c r="AA8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 47571-2025 FSC-klagomål.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AB7">
+      <c r="AB8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 47571-2025 FSC-klagomål mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AC7">
+      <c r="AC8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 47571-2025 tillsynsbegäran.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AD7">
+      <c r="AD8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 47571-2025 tillsynsbegäran mail.docx", "A 47571-2025")</f>
         <v/>
       </c>
-      <c r="AE7">
+      <c r="AE8">
         <f>HYPERLINK("https://klasma.github.io/Logging_1761/fåglar/A 47571-2025 prioriterade fågelarter.docx", "A 47571-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8" ht="15" customHeight="1">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>A 61380-2023</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>45264</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46324</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>VÄRMLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>HAMMARÖ</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" t="n">
-        <v>1</v>
-      </c>
-      <c r="L8" t="n">
-        <v>3</v>
-      </c>
-      <c r="M8" t="n">
-        <v>1</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>5</v>
-      </c>
-      <c r="T8" t="n">
-        <v>8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>4</v>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Blå taggsvamp
-Gropticka
-Motaggsvamp
-Gullgröppa</t>
-        </is>
-      </c>
-      <c r="W8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 61380-2023 artfynd.xlsx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="X8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 61380-2023 karta.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Y8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 61380-2023 georefererad karta.tif", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="Z8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 61380-2023 karta knärot.png", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AA8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 61380-2023 FSC-klagomål.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AB8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 61380-2023 FSC-klagomål mail.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AC8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 61380-2023 tillsynsbegäran.docx", "A 61380-2023")</f>
-        <v/>
-      </c>
-      <c r="AD8">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 61380-2023 tillsynsbegäran mail.docx", "A 61380-2023")</f>
         <v/>
       </c>
     </row>
@@ -1418,7 +1418,7 @@
         <v>44727</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         <v>44727</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         <v>45980</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 2769-2023</t>
+          <t>A 41899-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44944</v>
+        <v>45176</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1784,17 +1784,22 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I12" t="n">
-        <v>8.699999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1809,7 +1814,7 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1818,49 +1823,49 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="W12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="X12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="Y12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AA12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AB12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AC12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
         <v/>
       </c>
       <c r="AD12">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 55068-2023</t>
+          <t>A 58382-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1874,10 +1879,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1889,25 +1894,20 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1922,55 +1922,59 @@
         <v>1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="X13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="Y13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
+        <v/>
+      </c>
+      <c r="Z13">
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AA13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AB13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AC13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
         <v/>
       </c>
       <c r="AD13">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 41899-2023</t>
+          <t>A 53276-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1980,14 +1984,14 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45176</v>
+        <v>45229</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2005,7 +2009,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.8</v>
+        <v>0.3</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2045,42 +2049,42 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="W14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 41899-2023 artfynd.xlsx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="X14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 41899-2023 karta.png", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="Y14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 41899-2023 georefererad karta.tif", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AA14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 41899-2023 FSC-klagomål.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AB14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 41899-2023 FSC-klagomål mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AC14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 41899-2023 tillsynsbegäran.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
         <v/>
       </c>
       <c r="AD14">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 41899-2023 tillsynsbegäran mail.docx", "A 41899-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 58382-2024</t>
+          <t>A 2769-2023</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2094,10 +2098,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45632</v>
+        <v>44944</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2110,19 +2114,19 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
@@ -2137,59 +2141,55 @@
         <v>1</v>
       </c>
       <c r="R15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
       </c>
       <c r="T15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 58382-2024 artfynd.xlsx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 2769-2023 artfynd.xlsx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="X15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 58382-2024 karta.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 2769-2023 karta.png", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="Y15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 58382-2024 georefererad karta.tif", "A 58382-2024")</f>
-        <v/>
-      </c>
-      <c r="Z15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/knärot/A 58382-2024 karta knärot.png", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 2769-2023 georefererad karta.tif", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AA15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 58382-2024 FSC-klagomål.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 2769-2023 FSC-klagomål.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AB15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 58382-2024 FSC-klagomål mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 2769-2023 FSC-klagomål mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AC15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 58382-2024 tillsynsbegäran.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 2769-2023 tillsynsbegäran.docx", "A 2769-2023")</f>
         <v/>
       </c>
       <c r="AD15">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 58382-2024 tillsynsbegäran mail.docx", "A 58382-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 2769-2023 tillsynsbegäran mail.docx", "A 2769-2023")</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 53276-2023</t>
+          <t>A 55068-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2199,14 +2199,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45229</v>
+        <v>45237</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2220,20 +2220,20 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.3</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -2248,7 +2248,7 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -2264,42 +2264,42 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 53276-2023 artfynd.xlsx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/artfynd/A 55068-2023 artfynd.xlsx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="X16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 53276-2023 karta.png", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor/A 55068-2023 karta.png", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="Y16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 53276-2023 georefererad karta.tif", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/kartor_geotiff/A 55068-2023 georefererad karta.tif", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AA16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 53276-2023 FSC-klagomål.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomål/A 55068-2023 FSC-klagomål.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AB16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 53276-2023 FSC-klagomål mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/klagomålsmail/A 55068-2023 FSC-klagomål mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AC16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 53276-2023 tillsynsbegäran.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsyn/A 55068-2023 tillsynsbegäran.docx", "A 55068-2023")</f>
         <v/>
       </c>
       <c r="AD16">
-        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 53276-2023 tillsynsbegäran mail.docx", "A 53276-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_1761/tillsynsmail/A 55068-2023 tillsynsbegäran mail.docx", "A 55068-2023")</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58383-2024</t>
+          <t>A 42957-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45632</v>
+        <v>45182</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2328,8 +2328,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>1.6</v>
+        <v>0.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -2372,7 +2377,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42955-2023</t>
+          <t>A 55066-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2386,10 +2391,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2403,11 +2408,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2450,7 +2455,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 42960-2023</t>
+          <t>A 53369-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2464,10 +2469,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45182</v>
+        <v>45614</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2479,13 +2484,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>0.4</v>
+        <v>3.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2528,7 +2528,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55069-2023</t>
+          <t>A 58383-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45237</v>
+        <v>45632</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2557,13 +2557,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>3.2</v>
+        <v>1.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2606,7 +2601,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 51008-2023</t>
+          <t>A 42955-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2616,14 +2611,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45218</v>
+        <v>45182</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2637,11 +2632,11 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2684,7 +2679,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 41895-2023</t>
+          <t>A 42960-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45176</v>
+        <v>45182</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2719,7 +2714,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2762,7 +2757,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 42957-2023</t>
+          <t>A 55069-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2776,10 +2771,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45182</v>
+        <v>45237</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2793,11 +2788,11 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Övriga Aktiebolag</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.5</v>
+        <v>3.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2840,7 +2835,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 13354-2022</t>
+          <t>A 51008-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2850,14 +2845,14 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44645</v>
+        <v>45218</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2869,8 +2864,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2913,7 +2913,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37934-2024</t>
+          <t>A 41895-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2923,14 +2923,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45544</v>
+        <v>45176</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2942,8 +2942,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2986,7 +2991,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 56799-2022</t>
+          <t>A 13354-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3000,10 +3005,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44894</v>
+        <v>44645</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3016,7 +3021,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3059,7 +3064,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 13356-2022</t>
+          <t>A 37934-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3069,14 +3074,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44645</v>
+        <v>45544</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3089,7 +3094,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3132,7 +3137,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 42951-2023</t>
+          <t>A 56799-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3146,10 +3151,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45182</v>
+        <v>44894</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3161,13 +3166,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -3210,7 +3210,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 57893-2023</t>
+          <t>A 13356-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3224,10 +3224,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45247</v>
+        <v>44645</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3239,13 +3239,8 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>0.7</v>
+        <v>1.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -3288,7 +3283,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55066-2023</t>
+          <t>A 42951-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3302,10 +3297,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45237</v>
+        <v>45182</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3319,11 +3314,11 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Övriga Aktiebolag</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3366,7 +3361,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53369-2024</t>
+          <t>A 57893-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3380,10 +3375,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45614</v>
+        <v>45247</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3395,8 +3390,13 @@
           <t>HAMMARÖ</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>3.4</v>
+        <v>0.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -3456,7 +3456,7 @@
         <v>45415</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
